--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N91_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N91_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.86897331205727</v>
+        <v>9.728708163209307</v>
       </c>
       <c r="D2" t="n">
-        <v>58.48402952194759</v>
+        <v>9.503654797316484</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
